--- a/output/pdf_financials_xlsx/SKYG.xlsx
+++ b/output/pdf_financials_xlsx/SKYG.xlsx
@@ -5876,37 +5876,37 @@
         <v>0.326472</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.082442</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.092742</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.431051</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.535151</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.736258</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.932558</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.393318</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.665338</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.83503</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.88603</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.97733</v>
       </c>
     </row>
     <row r="93">
@@ -7359,7 +7359,7 @@
         <v>-0.580548</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>5.783914</v>
+        <v>5.598733</v>
       </c>
       <c r="Q118" s="3" t="n">
         <v>0.447222</v>
@@ -9671,7 +9671,11 @@
           <t>Reserves 9, 10</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10625,7 +10629,11 @@
           <t>Reserves 10, 11</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11310,7 +11318,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -11803,7 +11815,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -12805,7 +12821,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -13498,7 +13518,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -21796,7 +21820,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SKYG.xlsx
+++ b/output/pdf_financials_xlsx/SKYG.xlsx
@@ -1029,19 +1029,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000269</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000211</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.004609</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000822</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1977,19 +1977,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.081899</v>
+        <v>-0.082168</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.081773</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.515131</v>
+        <v>-0.515342</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.149623</v>
+        <v>-1.154232</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.538838</v>
+        <v>-2.53966</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.348573</v>
@@ -2093,19 +2093,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.081899</v>
+        <v>-0.082168</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.081773</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.515131</v>
+        <v>-0.515342</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.149095</v>
+        <v>-1.153704</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.538262</v>
+        <v>-2.539084</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.34796</v>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.176661</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.059055</v>
@@ -2415,40 +2415,40 @@
         <v>0.046901</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000283</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.192224</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.058888</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.140877</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.006961</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.595105</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.139958</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.011144</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.001681</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.003053</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.18979</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.022211</v>
       </c>
     </row>
     <row r="35">
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.176661</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.059055</v>
@@ -2531,40 +2531,40 @@
         <v>0.046901</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000283</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.192224</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.058888</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.140877</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.006961</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.595105</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.139958</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.011144</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.001681</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.003053</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.161</v>
+        <v>0.35079</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.0475</v>
+        <v>0.069711</v>
       </c>
     </row>
     <row r="37">
@@ -3227,40 +3227,40 @@
         <v>0.013681</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.002885</v>
+        <v>0.002602</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.205939</v>
+        <v>0.013715</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.072246</v>
+        <v>0.013358</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.389077</v>
+        <v>0.2482</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.06810099999999999</v>
+        <v>0.06114</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.904272</v>
+        <v>0.309167</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.174958</v>
+        <v>0.035</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.036144</v>
+        <v>0.025</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.007001</v>
+        <v>0.00532</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.011496</v>
+        <v>0.008443000000000001</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.19309</v>
+        <v>0.0033</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.023136</v>
+        <v>0.000925</v>
       </c>
     </row>
     <row r="49">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
@@ -59844,7 +59844,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -63874,7 +63874,7 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E557" s="5" t="n">

--- a/output/pdf_financials_xlsx/SKYG.xlsx
+++ b/output/pdf_financials_xlsx/SKYG.xlsx
@@ -742,16 +742,16 @@
         <v>0.005908</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.014462</v>
+        <v>0.063793</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.092527</v>
+        <v>0.230062</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.290094</v>
+        <v>0.810549</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.062857</v>
+        <v>0.313334</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.119949</v>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.005943</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.049331</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -913,19 +913,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.005908</v>
+        <v>0.011851</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.014462</v>
+        <v>0.113124</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.092527</v>
+        <v>0.230062</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.376874</v>
+        <v>0.897329</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.071351</v>
+        <v>0.321828</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.156444</v>
@@ -3513,10 +3513,10 @@
         <v>0</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0</v>
+        <v>0.001189</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0</v>
+        <v>0.000613</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>0</v>
@@ -4482,10 +4482,10 @@
         <v>0</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0</v>
+        <v>0.05285</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0</v>
+        <v>0.05285</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>0</v>
@@ -4598,10 +4598,10 @@
         <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.05285</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.05285</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0</v>
@@ -4833,7 +4833,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.05285</v>
+        <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0.249081</v>
@@ -5139,15 +5139,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F80" s="3" t="n">
+        <v>-0.1193853855120131</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>-0.06694271299752623</v>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
@@ -5626,19 +5622,19 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>0.213242</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>0.213242</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>1.318743</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>3.528262</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>3.576098</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>3.576098</v>
@@ -5858,7 +5854,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.040034</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0.040034</v>
@@ -14819,7 +14815,11 @@
           <t>Equipment – Note 5</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -15213,7 +15213,11 @@
           <t>Loans payable – Note 7</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -15409,7 +15413,11 @@
           <t>Share Capital – Note 8</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -16623,7 +16631,11 @@
           <t>Share Capital – Note 8</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -17324,7 +17336,11 @@
           <t>Mineral properties- Note 3</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -17629,7 +17645,11 @@
           <t>Share capital – Note 5</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -17728,7 +17748,11 @@
           <t>Contributed surplus – Note 5</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -18235,7 +18259,11 @@
           <t>Share capital – Note 3</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>0.213242</v>
       </c>
@@ -18334,7 +18362,11 @@
           <t>Contributed surplus – Note 3</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
         <v>0.040034</v>
       </c>
@@ -58452,7 +58484,11 @@
           <t>Consulting fees – Note 9</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
           <t>-</t>
@@ -58846,7 +58882,11 @@
           <t>Legal fees – Note 9</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -62058,7 +62098,11 @@
           <t>Legal fees – Note 6</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E539" t="inlineStr">
         <is>
           <t>-</t>
@@ -63569,7 +63613,11 @@
           <t>Legal – Note 5</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E554" s="5" t="n">
         <v>0.005943</v>
       </c>

--- a/output/pdf_financials_xlsx/SKYG.xlsx
+++ b/output/pdf_financials_xlsx/SKYG.xlsx
@@ -4204,28 +4204,28 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.123322</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.118766</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.036644</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.008362</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.040535</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.070253</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.04077</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.107045</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>0</v>
@@ -4378,28 +4378,28 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.028769</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.024819</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.03194</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.078126</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>0</v>
@@ -6327,22 +6327,22 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00281</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003987</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.028118</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.069192</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.101816</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.001253</v>
       </c>
       <c r="H101" s="3" t="n">
         <v>0</v>
@@ -6617,22 +6617,22 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.012774</v>
+        <v>0.009964000000000001</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.006846</v>
+        <v>-0.010833</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.02674</v>
+        <v>-0.001378</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.11094</v>
+        <v>0.041748</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.103024</v>
+        <v>0.20484</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.022521</v>
+        <v>0.023774</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>-0.109319</v>
@@ -6867,10 +6867,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.022815</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.027433</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -23216,7 +23216,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -26491,7 +26495,11 @@
           <t>Convertible debenture – accretion expense</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -31458,7 +31466,11 @@
           <t>HST/GST receivable</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -32874,7 +32886,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -36423,7 +36439,11 @@
           <t>HST/GST receivable</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -37833,7 +37853,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E296" s="5" t="n">
         <v>-0.00281</v>
       </c>
